--- a/RMNACH - FMOH Use Case Prioritization Criteria.xlsx
+++ b/RMNACH - FMOH Use Case Prioritization Criteria.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Please suggest potential collaborators/institutions</t>
   </si>
   <si>
-    <t xml:space="preserve">FmoH/Haramaya University</t>
+    <t xml:space="preserve">MoH/Haramaya University</t>
   </si>
   <si>
     <t xml:space="preserve">RMNACH</t>
@@ -73,13 +73,13 @@
     <t xml:space="preserve">Perinatal health - identify stillbirth risk factors and predict risk in early pregnancy</t>
   </si>
   <si>
-    <t xml:space="preserve">Can routine maternal and facility data be used to identify high-risk populations and predict stillbirth risk early in pregnancy?</t>
+    <t xml:space="preserve">1. Can routine maternal and facility data be used to identify high-risk populations and predict stillbirth risk early in pregnancy?</t>
   </si>
   <si>
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">FMoH/Maternal health</t>
+    <t xml:space="preserve">MoH/Maternal health</t>
   </si>
   <si>
     <t xml:space="preserve">Obstetric fistula - estimate burden and identify access gaps in prevention and treatment services</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">Uterovaginal prolapse - estimate prevalence and incidence at national and sub-regional levels</t>
   </si>
   <si>
-    <t xml:space="preserve">What is  the estimated prevalence and incidence of uterovaginal prolapse at national and sub-regional levels?</t>
+    <t xml:space="preserve">1. What is the estimated prevalence and incidence of uterovaginal prolapse at national and sub-regional levels?</t>
   </si>
   <si>
     <t xml:space="preserve">no</t>
@@ -124,7 +124,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +191,12 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -252,7 +258,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -298,6 +304,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -634,25 +644,25 @@
       <c r="C3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>21</v>
       </c>
       <c r="K3" s="4" t="s">
@@ -672,25 +682,25 @@
       <c r="C4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="4" t="s">
